--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_28-12-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_28-12-2025.xlsx
@@ -655,7 +655,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>£11.40</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>£39.38</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
